--- a/entertainment_forms/008_livestream_broadcast_license_application_form--entertainment_forms.xlsx
+++ b/entertainment_forms/008_livestream_broadcast_license_application_form--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>tiktok</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>content_target_platform_choices</t>
+          <t>content_target_country_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>united_states</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>united_states</t>
+          <t>australia</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>australia</t>
+          <t>united_kingdom</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United Kingdom</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>united_kingdom</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>canada</t>
+          <t>japan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Japan</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>japan</t>
+          <t>china</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
     </row>
@@ -1607,29 +1607,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>china</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>content_target_country_choices</t>
+          <t>content_target_language_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>japanese</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>Japanese</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>japanese</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>Chinese</t>
         </is>
       </c>
     </row>
@@ -1709,29 +1709,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>content_target_language_choices</t>
+          <t>content_target_audience_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1760,27 +1760,10 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>private</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>content_target_audience_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>paid</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
         <is>
           <t>Paid</t>
         </is>
